--- a/EST.xlsx
+++ b/EST.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E14E41B-5B99-F542-9F4F-43DCAD73855D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1764CE98-FEDE-4390-A7C3-DED39581C812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EST" sheetId="1" r:id="rId1"/>
@@ -139,9 +139,6 @@
     <t>8.50kg</t>
   </si>
   <si>
-    <t>2.90kg</t>
-  </si>
-  <si>
     <t>11.00kg</t>
   </si>
   <si>
@@ -206,6 +203,9 @@
   </si>
   <si>
     <t>KU_</t>
+  </si>
+  <si>
+    <t>2.20kg</t>
   </si>
 </sst>
 </file>
@@ -495,8 +495,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Çıkış" xfId="1" builtinId="21"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Output" xfId="1" builtinId="21"/>
   </cellStyles>
   <dxfs count="19">
     <dxf>
@@ -1174,7 +1174,7 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Kalınlık" dataDxfId="11"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Astar Boyu" dataDxfId="10"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Taban Boyu" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{390BAC77-C30D-6A43-92B0-DC5749F44257}" name="Ağız Çapı" dataDxfId="8" dataCellStyle="Output"/>
+    <tableColumn id="14" xr3:uid="{390BAC77-C30D-6A43-92B0-DC5749F44257}" name="Ağız Çapı" dataDxfId="8"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Astar Ağırlık" dataDxfId="7"/>
     <tableColumn id="8" xr3:uid="{A009F055-9F4E-4939-80FA-CF766AEF6E7A}" name="Kulp Tip" dataDxfId="6"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Kulp Ağırlık" dataDxfId="5"/>
@@ -1479,23 +1479,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="97" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="98.25" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>2</v>
@@ -1541,15 +1541,15 @@
         <v>20</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="17" t="s">
-        <v>32</v>
-      </c>
     </row>
-    <row r="3" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1563,18 +1563,18 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>10</v>
@@ -1586,13 +1586,13 @@
         <v>16</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="4" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="K4" s="3">
         <v>6</v>
@@ -1601,18 +1601,18 @@
         <v>21</v>
       </c>
       <c r="M4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="11" t="s">
-        <v>39</v>
-      </c>
     </row>
-    <row r="5" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>11</v>
@@ -1621,10 +1621,10 @@
         <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1639,18 +1639,18 @@
         <v>22</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>11</v>
@@ -1675,18 +1675,18 @@
         <v>23</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>11</v>
@@ -1713,18 +1713,18 @@
         <v>24</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>11</v>
@@ -1736,7 +1736,7 @@
       <c r="H8" s="13"/>
       <c r="I8" s="13"/>
       <c r="J8" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K8" s="13">
         <v>6</v>
@@ -1745,13 +1745,13 @@
         <v>25</v>
       </c>
       <c r="M8" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -1762,19 +1762,19 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:14" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="J15" s="6"/>
     </row>
   </sheetData>
